--- a/output/pdf_financials_xlsx/WAVE.xlsx
+++ b/output/pdf_financials_xlsx/WAVE.xlsx
@@ -1865,28 +1865,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.856242</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.942968</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.477417</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.133797</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.053015</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.235929</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.04495</v>
       </c>
     </row>
     <row r="35">
@@ -1927,28 +1927,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.856242</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.942968</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.477417</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.133797</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.053015</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.235929</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.04495</v>
       </c>
     </row>
     <row r="37">
@@ -2299,28 +2299,28 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
         <v>0.0171</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>3.297186</v>
+        <v>0.354218</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2.451459</v>
+        <v>0.974042</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.3776</v>
+        <v>0.243803</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.277895</v>
+        <v>0.22488</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.259554</v>
+        <v>0.023625</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.081078</v>
+        <v>0.036128</v>
       </c>
     </row>
     <row r="49">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">

--- a/output/pdf_financials_xlsx/WAVE.xlsx
+++ b/output/pdf_financials_xlsx/WAVE.xlsx
@@ -3929,16 +3929,16 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.107725</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.321905</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.015928</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.054618</v>
       </c>
     </row>
     <row r="101">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -14206,7 +14206,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">

--- a/output/pdf_financials_xlsx/WAVE.xlsx
+++ b/output/pdf_financials_xlsx/WAVE.xlsx
@@ -3015,10 +3015,10 @@
         <v>0</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0</v>
+        <v>0.037116</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.045532</v>
       </c>
     </row>
     <row r="71">
@@ -3046,10 +3046,10 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.037116</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.045532</v>
       </c>
     </row>
     <row r="72">
@@ -3170,10 +3170,10 @@
         <v>1.602059</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>2.847499</v>
+        <v>2.810383</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>3.266309</v>
+        <v>3.220777</v>
       </c>
     </row>
     <row r="76">
@@ -3334,15 +3334,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>-0.01826968608390982</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>-0.0160718212601124</v>
       </c>
     </row>
     <row r="81">
@@ -4013,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.0171</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>-0.008891</v>
@@ -4106,7 +4102,7 @@
         <v>0.001078</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.055789</v>
+        <v>0.038689</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>-0.283886</v>
@@ -5944,7 +5940,11 @@
           <t>Current portion of lease obligation 11</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -17306,7 +17306,11 @@
           <t>Prepaid expenses and other current assets</t>
         </is>
       </c>
-      <c r="D225" t="inlineStr"/>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E225" t="inlineStr">
         <is>
           <t>-</t>
